--- a/data-siswa.xlsx
+++ b/data-siswa.xlsx
@@ -363,10 +363,10 @@
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
     </row>
